--- a/test/inputs/case_NL/NL_HV_Network.xlsx
+++ b/test/inputs/case_NL/NL_HV_Network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomyk\Desktop\Julia\Network Reduction Model NL Data Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomyk\Desktop\Network Reduction Model\NetworkReduction.jl\test\inputs\case_NL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10A078B-0C7F-4D60-8A0A-0F871623B861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229403BD-FCCF-4BD0-B046-53B96063F51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB6C70BB-D278-43BD-BF3B-541149093B82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{EB6C70BB-D278-43BD-BF3B-541149093B82}"/>
   </bookViews>
   <sheets>
     <sheet name="Lines" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Generators" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Nodes!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Nodes!$A$1:$P$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="258">
   <si>
     <t>EIC_Code</t>
   </si>
@@ -813,6 +813,9 @@
   </si>
   <si>
     <t>Capacity_MW</t>
+  </si>
+  <si>
+    <t>IsRepresentative</t>
   </si>
 </sst>
 </file>
@@ -940,7 +943,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -973,8 +976,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4486,1901 +4488,1923 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CBED238-7D8E-4E5A-8A55-C5BC7EDC270C}">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="9.140625" style="23"/>
-    <col min="10" max="10" width="14.85546875" style="23" customWidth="1"/>
-    <col min="11" max="11" width="24.85546875" style="23" customWidth="1"/>
-    <col min="12" max="13" width="9.140625" style="23"/>
-    <col min="14" max="14" width="20.5703125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" style="23" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="22" t="s">
         <v>221</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="23">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2" s="23">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23">
-        <v>0</v>
-      </c>
-      <c r="F2" s="23">
-        <v>0</v>
-      </c>
-      <c r="G2" s="23" t="s">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>255</v>
       </c>
-      <c r="H2" s="23">
+      <c r="I2">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I2" s="23">
+      <c r="J2">
         <v>21.92</v>
       </c>
-      <c r="J2" s="23">
+      <c r="K2">
         <v>138</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="L2" t="s">
         <v>226</v>
       </c>
-      <c r="L2" s="23">
+      <c r="M2">
         <v>1.06</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="N2" t="s">
         <v>218</v>
       </c>
-      <c r="N2" s="23">
+      <c r="O2">
         <v>52.338992599999997</v>
       </c>
-      <c r="O2" s="23">
+      <c r="P2">
         <v>4.9591887999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="23">
-        <v>0</v>
-      </c>
-      <c r="D3" s="23">
-        <v>0</v>
-      </c>
-      <c r="E3" s="23">
-        <v>0</v>
-      </c>
-      <c r="F3" s="23">
-        <v>0</v>
-      </c>
-      <c r="G3" s="23" t="s">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>255</v>
       </c>
-      <c r="H3" s="23">
+      <c r="I3">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I3" s="23">
+      <c r="J3">
         <v>21.92</v>
       </c>
-      <c r="J3" s="23">
+      <c r="K3">
         <v>138</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="L3" t="s">
         <v>226</v>
       </c>
-      <c r="L3" s="23">
+      <c r="M3">
         <v>2.06</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="N3" t="s">
         <v>218</v>
       </c>
-      <c r="N3" s="23">
+      <c r="O3">
         <v>52.352427499999997</v>
       </c>
-      <c r="O3" s="23">
+      <c r="P3">
         <v>4.6825852000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="23">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="C4" s="23">
-        <v>0</v>
-      </c>
-      <c r="D4" s="23">
-        <v>0</v>
-      </c>
-      <c r="E4" s="23">
-        <v>0</v>
-      </c>
-      <c r="F4" s="23">
-        <v>0</v>
-      </c>
-      <c r="G4" s="23" t="s">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>255</v>
       </c>
-      <c r="H4" s="23">
+      <c r="I4">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I4" s="23">
+      <c r="J4">
         <v>21.92</v>
       </c>
-      <c r="J4" s="23">
+      <c r="K4">
         <v>138</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="L4" t="s">
         <v>226</v>
       </c>
-      <c r="L4" s="23">
+      <c r="M4">
         <v>3.06</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="N4" t="s">
         <v>218</v>
       </c>
-      <c r="N4" s="23">
+      <c r="O4">
         <v>52.486984200000002</v>
       </c>
-      <c r="O4" s="23">
+      <c r="P4">
         <v>4.6574467999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="23">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5" s="23">
-        <v>0</v>
-      </c>
-      <c r="D5" s="23">
-        <v>0</v>
-      </c>
-      <c r="E5" s="23">
-        <v>0</v>
-      </c>
-      <c r="F5" s="23">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="s">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
         <v>255</v>
       </c>
-      <c r="H5" s="23">
+      <c r="I5">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I5" s="23">
+      <c r="J5">
         <v>21.92</v>
       </c>
-      <c r="J5" s="23">
+      <c r="K5">
         <v>138</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="L5" t="s">
         <v>226</v>
       </c>
-      <c r="L5" s="23">
+      <c r="M5">
         <v>4.0599999999999996</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="N5" t="s">
         <v>218</v>
       </c>
-      <c r="N5" s="23">
+      <c r="O5">
         <v>52.440497200000003</v>
       </c>
-      <c r="O5" s="23">
+      <c r="P5">
         <v>4.8757219000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="23">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="C6" s="23">
-        <v>0</v>
-      </c>
-      <c r="D6" s="23">
-        <v>0</v>
-      </c>
-      <c r="E6" s="23">
-        <v>0</v>
-      </c>
-      <c r="F6" s="23">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="s">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
         <v>255</v>
       </c>
-      <c r="H6" s="23">
+      <c r="I6">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I6" s="23">
+      <c r="J6">
         <v>21.92</v>
       </c>
-      <c r="J6" s="23">
+      <c r="K6">
         <v>138</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="L6" t="s">
         <v>227</v>
       </c>
-      <c r="L6" s="23">
+      <c r="M6">
         <v>5.0599999999999996</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="N6" t="s">
         <v>218</v>
       </c>
-      <c r="N6" s="23">
+      <c r="O6">
         <v>51.91</v>
       </c>
-      <c r="O6" s="23">
+      <c r="P6">
         <v>4.63</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="23">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="C7" s="23">
-        <v>0</v>
-      </c>
-      <c r="D7" s="23">
-        <v>0</v>
-      </c>
-      <c r="E7" s="23">
-        <v>0</v>
-      </c>
-      <c r="F7" s="23">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23" t="s">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
         <v>255</v>
       </c>
-      <c r="H7" s="23">
+      <c r="I7">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I7" s="23">
+      <c r="J7">
         <v>21.92</v>
       </c>
-      <c r="J7" s="23">
+      <c r="K7">
         <v>138</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="L7" t="s">
         <v>227</v>
       </c>
-      <c r="L7" s="23">
+      <c r="M7">
         <v>6.06</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="N7" t="s">
         <v>218</v>
       </c>
-      <c r="N7" s="23">
+      <c r="O7">
         <v>51.817118100000002</v>
       </c>
-      <c r="O7" s="23">
+      <c r="P7">
         <v>4.7458194999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="23">
-        <v>0</v>
-      </c>
-      <c r="D8" s="23">
-        <v>0</v>
-      </c>
-      <c r="E8" s="23">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
         <v>255</v>
       </c>
-      <c r="H8" s="23">
+      <c r="I8">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I8" s="23">
+      <c r="J8">
         <v>21.92</v>
       </c>
-      <c r="J8" s="23">
+      <c r="K8">
         <v>138</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="L8" t="s">
         <v>227</v>
       </c>
-      <c r="L8" s="23">
+      <c r="M8">
         <v>7.06</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="N8" t="s">
         <v>218</v>
       </c>
-      <c r="N8" s="23">
+      <c r="O8">
         <v>51.940493060000001</v>
       </c>
-      <c r="O8" s="23">
+      <c r="P8">
         <v>4.0679207369999997</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="23">
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="C9" s="23">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23">
-        <v>0</v>
-      </c>
-      <c r="E9" s="23">
-        <v>0</v>
-      </c>
-      <c r="F9" s="23">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23" t="s">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
         <v>255</v>
       </c>
-      <c r="H9" s="23">
+      <c r="I9">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I9" s="23">
+      <c r="J9">
         <v>21.92</v>
       </c>
-      <c r="J9" s="23">
+      <c r="K9">
         <v>138</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="L9" t="s">
         <v>227</v>
       </c>
-      <c r="L9" s="23">
+      <c r="M9">
         <v>8.06</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="N9" t="s">
         <v>218</v>
       </c>
-      <c r="N9" s="23">
+      <c r="O9">
         <v>52.007583740000001</v>
       </c>
-      <c r="O9" s="23">
+      <c r="P9">
         <v>4.3223062590000003</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="23">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C10" s="23">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23">
-        <v>0</v>
-      </c>
-      <c r="E10" s="23">
-        <v>0</v>
-      </c>
-      <c r="F10" s="23">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23" t="s">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
         <v>255</v>
       </c>
-      <c r="H10" s="23">
+      <c r="I10">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I10" s="23">
+      <c r="J10">
         <v>21.92</v>
       </c>
-      <c r="J10" s="23">
+      <c r="K10">
         <v>138</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="L10" t="s">
         <v>227</v>
       </c>
-      <c r="L10" s="23">
+      <c r="M10">
         <v>9.06</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="N10" t="s">
         <v>218</v>
       </c>
-      <c r="N10" s="23">
+      <c r="O10">
         <v>52.009479900000002</v>
       </c>
-      <c r="O10" s="23">
+      <c r="P10">
         <v>4.5384196000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="23">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="C11" s="23">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23">
-        <v>0</v>
-      </c>
-      <c r="E11" s="23">
-        <v>0</v>
-      </c>
-      <c r="F11" s="23">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23" t="s">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
         <v>255</v>
       </c>
-      <c r="H11" s="23">
+      <c r="I11">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I11" s="23">
+      <c r="J11">
         <v>21.92</v>
       </c>
-      <c r="J11" s="23">
+      <c r="K11">
         <v>138</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="L11" t="s">
         <v>227</v>
       </c>
-      <c r="L11" s="23">
+      <c r="M11">
         <v>10.06</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="N11" t="s">
         <v>218</v>
       </c>
-      <c r="N11" s="23">
+      <c r="O11">
         <v>51.968447509999997</v>
       </c>
-      <c r="O11" s="23">
+      <c r="P11">
         <v>4.2188747830000004</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="23">
+      <c r="C12">
         <v>3</v>
       </c>
-      <c r="C12" s="23">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23">
-        <v>0</v>
-      </c>
-      <c r="E12" s="23">
-        <v>0</v>
-      </c>
-      <c r="F12" s="23">
-        <v>0</v>
-      </c>
-      <c r="G12" s="23" t="s">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
         <v>255</v>
       </c>
-      <c r="H12" s="23">
+      <c r="I12">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I12" s="23">
+      <c r="J12">
         <v>21.92</v>
       </c>
-      <c r="J12" s="23">
+      <c r="K12">
         <v>138</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="L12" t="s">
         <v>227</v>
       </c>
-      <c r="L12" s="23">
+      <c r="M12">
         <v>11.06</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="N12" t="s">
         <v>218</v>
       </c>
-      <c r="N12" s="23">
+      <c r="O12">
         <v>51.821815000000001</v>
       </c>
-      <c r="O12" s="23">
+      <c r="P12">
         <v>4.2898094999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
         <v>118</v>
       </c>
-      <c r="B13" s="23">
+      <c r="C13">
         <v>1</v>
       </c>
-      <c r="C13" s="23">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23">
-        <v>0</v>
-      </c>
-      <c r="E13" s="23">
-        <v>0</v>
-      </c>
-      <c r="F13" s="23">
-        <v>0</v>
-      </c>
-      <c r="G13" s="23" t="s">
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
         <v>255</v>
       </c>
-      <c r="H13" s="23">
+      <c r="I13">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I13" s="23">
+      <c r="J13">
         <v>21.92</v>
       </c>
-      <c r="J13" s="23">
+      <c r="K13">
         <v>138</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="L13" t="s">
         <v>222</v>
       </c>
-      <c r="L13" s="23">
+      <c r="M13">
         <v>13.06</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="N13" t="s">
         <v>218</v>
       </c>
-      <c r="N13" s="23">
+      <c r="O13">
         <v>51.425664500000003</v>
       </c>
-      <c r="O13" s="23">
+      <c r="P13">
         <v>3.7336697000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="23">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23">
-        <v>0</v>
-      </c>
-      <c r="E14" s="23">
-        <v>0</v>
-      </c>
-      <c r="F14" s="23">
-        <v>0</v>
-      </c>
-      <c r="G14" s="23" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
         <v>255</v>
       </c>
-      <c r="H14" s="23">
+      <c r="I14">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I14" s="23">
+      <c r="J14">
         <v>21.92</v>
       </c>
-      <c r="J14" s="23">
+      <c r="K14">
         <v>138</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="L14" t="s">
         <v>222</v>
       </c>
-      <c r="L14" s="23">
+      <c r="M14">
         <v>14.06</v>
       </c>
-      <c r="M14" s="23" t="s">
+      <c r="N14" t="s">
         <v>218</v>
       </c>
-      <c r="N14" s="23">
+      <c r="O14">
         <v>51.42054023</v>
       </c>
-      <c r="O14" s="23">
+      <c r="P14">
         <v>4.2356474549999996</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:16">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="23">
+      <c r="C15">
         <v>1</v>
       </c>
-      <c r="C15" s="23">
-        <v>0</v>
-      </c>
-      <c r="D15" s="23">
-        <v>0</v>
-      </c>
-      <c r="E15" s="23">
-        <v>0</v>
-      </c>
-      <c r="F15" s="23">
-        <v>0</v>
-      </c>
-      <c r="G15" s="23" t="s">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
         <v>255</v>
       </c>
-      <c r="H15" s="23">
+      <c r="I15">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I15" s="23">
+      <c r="J15">
         <v>21.92</v>
       </c>
-      <c r="J15" s="23">
+      <c r="K15">
         <v>138</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="L15" t="s">
         <v>225</v>
       </c>
-      <c r="L15" s="23">
+      <c r="M15">
         <v>15.06</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="N15" t="s">
         <v>218</v>
       </c>
-      <c r="N15" s="23">
+      <c r="O15">
         <v>51.646971299999997</v>
       </c>
-      <c r="O15" s="23">
+      <c r="P15">
         <v>5.915710078</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="23" t="s">
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="23">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="C16" s="23">
-        <v>0</v>
-      </c>
-      <c r="D16" s="23">
-        <v>0</v>
-      </c>
-      <c r="E16" s="23">
-        <v>0</v>
-      </c>
-      <c r="F16" s="23">
-        <v>0</v>
-      </c>
-      <c r="G16" s="23" t="s">
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
         <v>255</v>
       </c>
-      <c r="H16" s="23">
+      <c r="I16">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I16" s="23">
+      <c r="J16">
         <v>21.92</v>
       </c>
-      <c r="J16" s="23">
+      <c r="K16">
         <v>138</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="L16" t="s">
         <v>225</v>
       </c>
-      <c r="L16" s="23">
+      <c r="M16">
         <v>16.059999999999999</v>
       </c>
-      <c r="M16" s="23" t="s">
+      <c r="N16" t="s">
         <v>218</v>
       </c>
-      <c r="N16" s="23">
+      <c r="O16">
         <v>51.423142300000002</v>
       </c>
-      <c r="O16" s="23">
+      <c r="P16">
         <v>5.4622897000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
-      <c r="A17" s="23" t="s">
+    <row r="17" spans="1:16">
+      <c r="A17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="23">
-        <v>0</v>
-      </c>
-      <c r="D17" s="23">
-        <v>0</v>
-      </c>
-      <c r="E17" s="23">
-        <v>0</v>
-      </c>
-      <c r="F17" s="23">
-        <v>0</v>
-      </c>
-      <c r="G17" s="23" t="s">
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
         <v>255</v>
       </c>
-      <c r="H17" s="23">
+      <c r="I17">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I17" s="23">
+      <c r="J17">
         <v>21.92</v>
       </c>
-      <c r="J17" s="23">
+      <c r="K17">
         <v>138</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="L17" t="s">
         <v>225</v>
       </c>
-      <c r="L17" s="23">
+      <c r="M17">
         <v>17.059999999999999</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="N17" t="s">
         <v>218</v>
       </c>
-      <c r="N17" s="23">
+      <c r="O17">
         <v>51.702365899999997</v>
       </c>
-      <c r="O17" s="23">
+      <c r="P17">
         <v>4.8499781000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:16">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="23">
-        <v>0</v>
-      </c>
-      <c r="D18" s="23">
-        <v>0</v>
-      </c>
-      <c r="E18" s="23">
-        <v>0</v>
-      </c>
-      <c r="F18" s="23">
-        <v>0</v>
-      </c>
-      <c r="G18" s="23" t="s">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
         <v>255</v>
       </c>
-      <c r="H18" s="23">
+      <c r="I18">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I18" s="23">
+      <c r="J18">
         <v>21.92</v>
       </c>
-      <c r="J18" s="23">
+      <c r="K18">
         <v>138</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="L18" t="s">
         <v>223</v>
       </c>
-      <c r="L18" s="23">
+      <c r="M18">
         <v>18.059999999999999</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="N18" t="s">
         <v>218</v>
       </c>
-      <c r="N18" s="23">
+      <c r="O18">
         <v>51.140410099999997</v>
       </c>
-      <c r="O18" s="23">
+      <c r="P18">
         <v>5.8885829999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:16">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="23">
+      <c r="C19">
         <v>1</v>
       </c>
-      <c r="C19" s="23">
-        <v>0</v>
-      </c>
-      <c r="D19" s="23">
-        <v>0</v>
-      </c>
-      <c r="E19" s="23">
-        <v>0</v>
-      </c>
-      <c r="F19" s="23">
-        <v>0</v>
-      </c>
-      <c r="G19" s="23" t="s">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
         <v>255</v>
       </c>
-      <c r="H19" s="23">
+      <c r="I19">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I19" s="23">
+      <c r="J19">
         <v>21.92</v>
       </c>
-      <c r="J19" s="23">
+      <c r="K19">
         <v>138</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="L19" t="s">
         <v>224</v>
       </c>
-      <c r="L19" s="23">
+      <c r="M19">
         <v>27.06</v>
       </c>
-      <c r="M19" s="23" t="s">
+      <c r="N19" t="s">
         <v>218</v>
       </c>
-      <c r="N19" s="23">
+      <c r="O19">
         <v>53.211991699999999</v>
       </c>
-      <c r="O19" s="23">
+      <c r="P19">
         <v>6.4875749000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="23" t="s">
+    <row r="20" spans="1:16">
+      <c r="A20" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="23">
+      <c r="C20">
         <v>1</v>
       </c>
-      <c r="C20" s="23">
-        <v>0</v>
-      </c>
-      <c r="D20" s="23">
-        <v>0</v>
-      </c>
-      <c r="E20" s="23">
-        <v>0</v>
-      </c>
-      <c r="F20" s="23">
-        <v>0</v>
-      </c>
-      <c r="G20" s="23" t="s">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
         <v>255</v>
       </c>
-      <c r="H20" s="23">
+      <c r="I20">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I20" s="23">
+      <c r="J20">
         <v>21.92</v>
       </c>
-      <c r="J20" s="23">
+      <c r="K20">
         <v>138</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="L20" t="s">
         <v>224</v>
       </c>
-      <c r="L20" s="23">
+      <c r="M20">
         <v>20.059999999999999</v>
       </c>
-      <c r="M20" s="23" t="s">
+      <c r="N20" t="s">
         <v>218</v>
       </c>
-      <c r="N20" s="23">
+      <c r="O20">
         <v>53.44</v>
       </c>
-      <c r="O20" s="23">
+      <c r="P20">
         <v>6.87</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="23" t="s">
+    <row r="21" spans="1:16">
+      <c r="A21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="23">
+      <c r="C21">
         <v>1</v>
       </c>
-      <c r="C21" s="23">
-        <v>0</v>
-      </c>
-      <c r="D21" s="23">
-        <v>0</v>
-      </c>
-      <c r="E21" s="23">
-        <v>0</v>
-      </c>
-      <c r="F21" s="23">
-        <v>0</v>
-      </c>
-      <c r="G21" s="23" t="s">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="23">
+      <c r="I21">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I21" s="23">
+      <c r="J21">
         <v>21.92</v>
       </c>
-      <c r="J21" s="23">
+      <c r="K21">
         <v>138</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="L21" t="s">
         <v>224</v>
       </c>
-      <c r="L21" s="23">
+      <c r="M21">
         <v>21.06</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="N21" t="s">
         <v>218</v>
       </c>
-      <c r="N21" s="23">
+      <c r="O21">
         <v>53.1765963</v>
       </c>
-      <c r="O21" s="23">
+      <c r="P21">
         <v>5.8840685060000002</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="23" t="s">
+    <row r="22" spans="1:16">
+      <c r="A22" t="s">
         <v>133</v>
       </c>
-      <c r="B22" s="23">
+      <c r="C22">
         <v>1</v>
       </c>
-      <c r="C22" s="23">
-        <v>0</v>
-      </c>
-      <c r="D22" s="23">
-        <v>0</v>
-      </c>
-      <c r="E22" s="23">
-        <v>0</v>
-      </c>
-      <c r="F22" s="23">
-        <v>0</v>
-      </c>
-      <c r="G22" s="23" t="s">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
         <v>255</v>
       </c>
-      <c r="H22" s="23">
+      <c r="I22">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I22" s="23">
+      <c r="J22">
         <v>21.92</v>
       </c>
-      <c r="J22" s="23">
+      <c r="K22">
         <v>138</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="L22" t="s">
         <v>224</v>
       </c>
-      <c r="L22" s="23">
+      <c r="M22">
         <v>22.06</v>
       </c>
-      <c r="M22" s="23" t="s">
+      <c r="N22" t="s">
         <v>218</v>
       </c>
-      <c r="N22" s="23">
+      <c r="O22">
         <v>52.956885800000002</v>
       </c>
-      <c r="O22" s="23">
+      <c r="P22">
         <v>5.8714262000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="23" t="s">
+    <row r="23" spans="1:16">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23" s="23">
-        <v>0</v>
-      </c>
-      <c r="D23" s="23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="23">
-        <v>0</v>
-      </c>
-      <c r="G23" s="23" t="s">
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
         <v>255</v>
       </c>
-      <c r="H23" s="23">
+      <c r="I23">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I23" s="23">
+      <c r="J23">
         <v>21.92</v>
       </c>
-      <c r="J23" s="23">
+      <c r="K23">
         <v>138</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="L23" t="s">
         <v>224</v>
       </c>
-      <c r="L23" s="23">
+      <c r="M23">
         <v>23.06</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="N23" t="s">
         <v>218</v>
       </c>
-      <c r="N23" s="23">
+      <c r="O23">
         <v>53.193690099999998</v>
       </c>
-      <c r="O23" s="23">
+      <c r="P23">
         <v>5.9913641999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="23" t="s">
+    <row r="24" spans="1:16">
+      <c r="A24" t="s">
         <v>166</v>
       </c>
-      <c r="B24" s="23">
+      <c r="C24">
         <v>1</v>
       </c>
-      <c r="C24" s="23">
-        <v>0</v>
-      </c>
-      <c r="D24" s="23">
-        <v>0</v>
-      </c>
-      <c r="E24" s="23">
-        <v>0</v>
-      </c>
-      <c r="F24" s="23">
-        <v>0</v>
-      </c>
-      <c r="G24" s="23" t="s">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
         <v>255</v>
       </c>
-      <c r="H24" s="23">
+      <c r="I24">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I24" s="23">
+      <c r="J24">
         <v>21.92</v>
       </c>
-      <c r="J24" s="23">
+      <c r="K24">
         <v>138</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="L24" t="s">
         <v>224</v>
       </c>
-      <c r="L24" s="23">
+      <c r="M24">
         <v>24.06</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="N24" t="s">
         <v>218</v>
       </c>
-      <c r="N24" s="23">
+      <c r="O24">
         <v>52.996938669999999</v>
       </c>
-      <c r="O24" s="23">
+      <c r="P24">
         <v>6.5035368509999998</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="23" t="s">
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
         <v>171</v>
       </c>
-      <c r="B25" s="23">
+      <c r="C25">
         <v>1</v>
       </c>
-      <c r="C25" s="23">
-        <v>0</v>
-      </c>
-      <c r="D25" s="23">
-        <v>0</v>
-      </c>
-      <c r="E25" s="23">
-        <v>0</v>
-      </c>
-      <c r="F25" s="23">
-        <v>0</v>
-      </c>
-      <c r="G25" s="23" t="s">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
         <v>255</v>
       </c>
-      <c r="H25" s="23">
+      <c r="I25">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I25" s="23">
+      <c r="J25">
         <v>21.92</v>
       </c>
-      <c r="J25" s="23">
+      <c r="K25">
         <v>138</v>
       </c>
-      <c r="K25" s="23" t="s">
+      <c r="L25" t="s">
         <v>224</v>
       </c>
-      <c r="L25" s="23">
+      <c r="M25">
         <v>25.06</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="N25" t="s">
         <v>218</v>
       </c>
-      <c r="N25" s="23">
+      <c r="O25">
         <v>53.311281000000001</v>
       </c>
-      <c r="O25" s="23">
+      <c r="P25">
         <v>6.9483641</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="23" t="s">
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
         <v>156</v>
       </c>
-      <c r="B26" s="23">
+      <c r="C26">
         <v>1</v>
       </c>
-      <c r="C26" s="23">
-        <v>0</v>
-      </c>
-      <c r="D26" s="23">
-        <v>0</v>
-      </c>
-      <c r="E26" s="23">
-        <v>0</v>
-      </c>
-      <c r="F26" s="23">
-        <v>0</v>
-      </c>
-      <c r="G26" s="23" t="s">
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
         <v>255</v>
       </c>
-      <c r="H26" s="23">
+      <c r="I26">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I26" s="23">
+      <c r="J26">
         <v>21.92</v>
       </c>
-      <c r="J26" s="23">
+      <c r="K26">
         <v>138</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="L26" t="s">
         <v>224</v>
       </c>
-      <c r="L26" s="23">
+      <c r="M26">
         <v>26.06</v>
       </c>
-      <c r="M26" s="23" t="s">
+      <c r="N26" t="s">
         <v>218</v>
       </c>
-      <c r="N26" s="23">
+      <c r="O26">
         <v>53.438588699999997</v>
       </c>
-      <c r="O26" s="23">
+      <c r="P26">
         <v>6.8354936999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="23" t="s">
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="23">
+      <c r="C27">
         <v>1</v>
       </c>
-      <c r="C27" s="23">
-        <v>0</v>
-      </c>
-      <c r="D27" s="23">
-        <v>0</v>
-      </c>
-      <c r="E27" s="23">
-        <v>0</v>
-      </c>
-      <c r="F27" s="23">
-        <v>0</v>
-      </c>
-      <c r="G27" s="23" t="s">
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
         <v>255</v>
       </c>
-      <c r="H27" s="23">
+      <c r="I27">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I27" s="23">
+      <c r="J27">
         <v>21.92</v>
       </c>
-      <c r="J27" s="23">
+      <c r="K27">
         <v>138</v>
       </c>
-      <c r="K27" s="23" t="s">
+      <c r="L27" t="s">
         <v>224</v>
       </c>
-      <c r="L27" s="23">
+      <c r="M27">
         <v>19.059999999999999</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="N27" t="s">
         <v>218</v>
       </c>
-      <c r="N27" s="23">
+      <c r="O27">
         <v>53.438588699999997</v>
       </c>
-      <c r="O27" s="23">
+      <c r="P27">
         <v>6.8354936999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="23" t="s">
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="23">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="C28" s="23">
-        <v>0</v>
-      </c>
-      <c r="D28" s="23">
-        <v>0</v>
-      </c>
-      <c r="E28" s="23">
-        <v>0</v>
-      </c>
-      <c r="F28" s="23">
-        <v>0</v>
-      </c>
-      <c r="G28" s="23" t="s">
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
         <v>255</v>
       </c>
-      <c r="H28" s="23">
+      <c r="I28">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I28" s="23">
+      <c r="J28">
         <v>21.92</v>
       </c>
-      <c r="J28" s="23">
+      <c r="K28">
         <v>138</v>
       </c>
-      <c r="K28" s="23" t="s">
+      <c r="L28" t="s">
         <v>224</v>
       </c>
-      <c r="L28" s="23">
+      <c r="M28">
         <v>28.06</v>
       </c>
-      <c r="M28" s="23" t="s">
+      <c r="N28" t="s">
         <v>218</v>
       </c>
-      <c r="N28" s="23">
+      <c r="O28">
         <v>53.428100000000001</v>
       </c>
-      <c r="O28" s="23">
+      <c r="P28">
         <v>6.7714999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="23" t="s">
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="23">
+      <c r="C29">
         <v>1</v>
       </c>
-      <c r="C29" s="23">
-        <v>0</v>
-      </c>
-      <c r="D29" s="23">
-        <v>0</v>
-      </c>
-      <c r="E29" s="23">
-        <v>0</v>
-      </c>
-      <c r="F29" s="23">
-        <v>0</v>
-      </c>
-      <c r="G29" s="23" t="s">
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
         <v>255</v>
       </c>
-      <c r="H29" s="23">
+      <c r="I29">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I29" s="23">
+      <c r="J29">
         <v>21.92</v>
       </c>
-      <c r="J29" s="23">
+      <c r="K29">
         <v>138</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="L29" t="s">
         <v>224</v>
       </c>
-      <c r="L29" s="23">
+      <c r="M29">
         <v>29.06</v>
       </c>
-      <c r="M29" s="23" t="s">
+      <c r="N29" t="s">
         <v>218</v>
       </c>
-      <c r="N29" s="23">
+      <c r="O29">
         <v>53.138772500000002</v>
       </c>
-      <c r="O29" s="23">
+      <c r="P29">
         <v>6.9284995</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="23" t="s">
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="23">
+      <c r="C30">
         <v>1</v>
       </c>
-      <c r="C30" s="23">
-        <v>0</v>
-      </c>
-      <c r="D30" s="23">
-        <v>0</v>
-      </c>
-      <c r="E30" s="23">
-        <v>0</v>
-      </c>
-      <c r="F30" s="23">
-        <v>0</v>
-      </c>
-      <c r="G30" s="23" t="s">
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
         <v>255</v>
       </c>
-      <c r="H30" s="23">
+      <c r="I30">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I30" s="23">
+      <c r="J30">
         <v>21.92</v>
       </c>
-      <c r="J30" s="23">
+      <c r="K30">
         <v>138</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="L30" t="s">
         <v>224</v>
       </c>
-      <c r="L30" s="23">
+      <c r="M30">
         <v>30.06</v>
       </c>
-      <c r="M30" s="23" t="s">
+      <c r="N30" t="s">
         <v>218</v>
       </c>
-      <c r="N30" s="23">
+      <c r="O30">
         <v>53.438588699999997</v>
       </c>
-      <c r="O30" s="23">
+      <c r="P30">
         <v>6.8354936999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
         <v>182</v>
       </c>
-      <c r="B31" s="23">
+      <c r="C31">
         <v>1</v>
       </c>
-      <c r="C31" s="23">
-        <v>0</v>
-      </c>
-      <c r="D31" s="23">
-        <v>0</v>
-      </c>
-      <c r="E31" s="23">
-        <v>0</v>
-      </c>
-      <c r="F31" s="23">
-        <v>0</v>
-      </c>
-      <c r="G31" s="23" t="s">
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
         <v>255</v>
       </c>
-      <c r="H31" s="23">
+      <c r="I31">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I31" s="23">
+      <c r="J31">
         <v>21.92</v>
       </c>
-      <c r="J31" s="23">
+      <c r="K31">
         <v>138</v>
       </c>
-      <c r="K31" s="23" t="s">
+      <c r="L31" t="s">
         <v>224</v>
       </c>
-      <c r="L31" s="23">
+      <c r="M31">
         <v>31.06</v>
       </c>
-      <c r="M31" s="23" t="s">
+      <c r="N31" t="s">
         <v>218</v>
       </c>
-      <c r="N31" s="23">
+      <c r="O31">
         <v>53.319781120000002</v>
       </c>
-      <c r="O31" s="23">
+      <c r="P31">
         <v>6.9440982990000002</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="23">
+      <c r="C32">
         <v>1</v>
       </c>
-      <c r="C32" s="23">
-        <v>0</v>
-      </c>
-      <c r="D32" s="23">
-        <v>0</v>
-      </c>
-      <c r="E32" s="23">
-        <v>0</v>
-      </c>
-      <c r="F32" s="23">
-        <v>0</v>
-      </c>
-      <c r="G32" s="23" t="s">
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
         <v>255</v>
       </c>
-      <c r="H32" s="23">
+      <c r="I32">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I32" s="23">
+      <c r="J32">
         <v>21.92</v>
       </c>
-      <c r="J32" s="23">
+      <c r="K32">
         <v>138</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="L32" t="s">
         <v>228</v>
       </c>
-      <c r="L32" s="23">
+      <c r="M32">
         <v>32.06</v>
       </c>
-      <c r="M32" s="23" t="s">
+      <c r="N32" t="s">
         <v>218</v>
       </c>
-      <c r="N32" s="23">
+      <c r="O32">
         <v>52.482809439999997</v>
       </c>
-      <c r="O32" s="23">
+      <c r="P32">
         <v>6.147732038</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="23" t="s">
+    <row r="33" spans="1:16">
+      <c r="A33" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="23">
+      <c r="C33">
         <v>1</v>
       </c>
-      <c r="C33" s="23">
-        <v>0</v>
-      </c>
-      <c r="D33" s="23">
-        <v>0</v>
-      </c>
-      <c r="E33" s="23">
-        <v>0</v>
-      </c>
-      <c r="F33" s="23">
-        <v>0</v>
-      </c>
-      <c r="G33" s="23" t="s">
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
         <v>255</v>
       </c>
-      <c r="H33" s="23">
+      <c r="I33">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I33" s="23">
+      <c r="J33">
         <v>21.92</v>
       </c>
-      <c r="J33" s="23">
+      <c r="K33">
         <v>138</v>
       </c>
-      <c r="K33" s="23" t="s">
+      <c r="L33" t="s">
         <v>228</v>
       </c>
-      <c r="L33" s="23">
+      <c r="M33">
         <v>33.06</v>
       </c>
-      <c r="M33" s="23" t="s">
+      <c r="N33" t="s">
         <v>218</v>
       </c>
-      <c r="N33" s="23">
+      <c r="O33">
         <v>52.156830900000003</v>
       </c>
-      <c r="O33" s="23">
+      <c r="P33">
         <v>4.9842056000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="23">
+      <c r="C34">
         <v>1</v>
       </c>
-      <c r="C34" s="23">
-        <v>0</v>
-      </c>
-      <c r="D34" s="23">
-        <v>0</v>
-      </c>
-      <c r="E34" s="23">
-        <v>0</v>
-      </c>
-      <c r="F34" s="23">
-        <v>0</v>
-      </c>
-      <c r="G34" s="23" t="s">
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
         <v>255</v>
       </c>
-      <c r="H34" s="23">
+      <c r="I34">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I34" s="23">
+      <c r="J34">
         <v>21.92</v>
       </c>
-      <c r="J34" s="23">
+      <c r="K34">
         <v>138</v>
       </c>
-      <c r="K34" s="23" t="s">
+      <c r="L34" t="s">
         <v>228</v>
       </c>
-      <c r="L34" s="23">
+      <c r="M34">
         <v>34.06</v>
       </c>
-      <c r="M34" s="23" t="s">
+      <c r="N34" t="s">
         <v>218</v>
       </c>
-      <c r="N34" s="23">
+      <c r="O34">
         <v>51.910513600000002</v>
       </c>
-      <c r="O34" s="23">
+      <c r="P34">
         <v>5.6568202000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="23" t="s">
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="B35" s="23">
+      <c r="C35">
         <v>1</v>
       </c>
-      <c r="C35" s="23">
-        <v>0</v>
-      </c>
-      <c r="D35" s="23">
-        <v>0</v>
-      </c>
-      <c r="E35" s="23">
-        <v>0</v>
-      </c>
-      <c r="F35" s="23">
-        <v>0</v>
-      </c>
-      <c r="G35" s="23" t="s">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
         <v>255</v>
       </c>
-      <c r="H35" s="23">
+      <c r="I35">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I35" s="23">
+      <c r="J35">
         <v>21.92</v>
       </c>
-      <c r="J35" s="23">
+      <c r="K35">
         <v>138</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="L35" t="s">
         <v>228</v>
       </c>
-      <c r="L35" s="23">
+      <c r="M35">
         <v>35.06</v>
       </c>
-      <c r="M35" s="23" t="s">
+      <c r="N35" t="s">
         <v>218</v>
       </c>
-      <c r="N35" s="23">
+      <c r="O35">
         <v>51.98</v>
       </c>
-      <c r="O35" s="23">
+      <c r="P35">
         <v>6.25</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="23" t="s">
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="23">
+      <c r="C36">
         <v>1</v>
       </c>
-      <c r="C36" s="23">
-        <v>0</v>
-      </c>
-      <c r="D36" s="23">
-        <v>0</v>
-      </c>
-      <c r="E36" s="23">
-        <v>0</v>
-      </c>
-      <c r="F36" s="23">
-        <v>0</v>
-      </c>
-      <c r="G36" s="23" t="s">
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
         <v>255</v>
       </c>
-      <c r="H36" s="23">
+      <c r="I36">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I36" s="23">
+      <c r="J36">
         <v>21.92</v>
       </c>
-      <c r="J36" s="23">
+      <c r="K36">
         <v>138</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="L36" t="s">
         <v>228</v>
       </c>
-      <c r="L36" s="23">
+      <c r="M36">
         <v>36.06</v>
       </c>
-      <c r="M36" s="23" t="s">
+      <c r="N36" t="s">
         <v>218</v>
       </c>
-      <c r="N36" s="23">
+      <c r="O36">
         <v>52.518537000000002</v>
       </c>
-      <c r="O36" s="23">
+      <c r="P36">
         <v>5.4714219999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="23" t="s">
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
         <v>53</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B37">
         <v>1</v>
       </c>
-      <c r="C37" s="23">
-        <v>0</v>
-      </c>
-      <c r="D37" s="23">
-        <v>0</v>
-      </c>
-      <c r="E37" s="23">
-        <v>0</v>
-      </c>
-      <c r="F37" s="23">
-        <v>0</v>
-      </c>
-      <c r="G37" s="23" t="s">
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
         <v>255</v>
       </c>
-      <c r="H37" s="23">
+      <c r="I37">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I37" s="23">
+      <c r="J37">
         <v>21.92</v>
       </c>
-      <c r="J37" s="23">
+      <c r="K37">
         <v>138</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="L37" t="s">
         <v>228</v>
       </c>
-      <c r="L37" s="23">
+      <c r="M37">
         <v>37.06</v>
       </c>
-      <c r="M37" s="23" t="s">
+      <c r="N37" t="s">
         <v>218</v>
       </c>
-      <c r="N37" s="23">
+      <c r="O37">
         <v>52.618804269999998</v>
       </c>
-      <c r="O37" s="23">
+      <c r="P37">
         <v>5.7601147199999998</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
-      <c r="A38" s="23" t="s">
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
         <v>161</v>
       </c>
-      <c r="B38" s="23">
+      <c r="C38">
         <v>1</v>
       </c>
-      <c r="C38" s="23">
-        <v>0</v>
-      </c>
-      <c r="D38" s="23">
-        <v>0</v>
-      </c>
-      <c r="E38" s="23">
-        <v>0</v>
-      </c>
-      <c r="F38" s="23">
-        <v>0</v>
-      </c>
-      <c r="G38" s="23" t="s">
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
         <v>255</v>
       </c>
-      <c r="H38" s="23">
+      <c r="I38">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I38" s="23">
+      <c r="J38">
         <v>21.92</v>
       </c>
-      <c r="J38" s="23">
+      <c r="K38">
         <v>138</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="L38" t="s">
         <v>228</v>
       </c>
-      <c r="L38" s="23">
+      <c r="M38">
         <v>38.06</v>
       </c>
-      <c r="M38" s="23" t="s">
+      <c r="N38" t="s">
         <v>218</v>
       </c>
-      <c r="N38" s="23">
+      <c r="O38">
         <v>52.521861829999999</v>
       </c>
-      <c r="O38" s="23">
+      <c r="P38">
         <v>6.1501917219999997</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
-      <c r="A39" s="23" t="s">
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="23">
+      <c r="C39">
         <v>1</v>
       </c>
-      <c r="C39" s="23">
-        <v>0</v>
-      </c>
-      <c r="D39" s="23">
-        <v>0</v>
-      </c>
-      <c r="E39" s="23">
-        <v>0</v>
-      </c>
-      <c r="F39" s="23">
-        <v>0</v>
-      </c>
-      <c r="G39" s="23" t="s">
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
         <v>255</v>
       </c>
-      <c r="H39" s="23">
+      <c r="I39">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I39" s="23">
+      <c r="J39">
         <v>21.92</v>
       </c>
-      <c r="J39" s="23">
+      <c r="K39">
         <v>138</v>
       </c>
-      <c r="K39" s="23" t="s">
+      <c r="L39" t="s">
         <v>228</v>
       </c>
-      <c r="L39" s="23">
+      <c r="M39">
         <v>39.06</v>
       </c>
-      <c r="M39" s="23" t="s">
+      <c r="N39" t="s">
         <v>218</v>
       </c>
-      <c r="N39" s="23">
+      <c r="O39">
         <v>52.239605699999998</v>
       </c>
-      <c r="O39" s="23">
+      <c r="P39">
         <v>6.7347755500000002</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
-      <c r="A40" s="23" t="s">
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="23">
+      <c r="C40">
         <v>1</v>
       </c>
-      <c r="C40" s="23">
-        <v>0</v>
-      </c>
-      <c r="D40" s="23">
-        <v>0</v>
-      </c>
-      <c r="E40" s="23">
-        <v>0</v>
-      </c>
-      <c r="F40" s="23">
-        <v>0</v>
-      </c>
-      <c r="G40" s="23" t="s">
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
         <v>255</v>
       </c>
-      <c r="H40" s="23">
+      <c r="I40">
         <v>0.94899999999999995</v>
       </c>
-      <c r="I40" s="23">
+      <c r="J40">
         <v>21.92</v>
       </c>
-      <c r="J40" s="23">
+      <c r="K40">
         <v>138</v>
       </c>
-      <c r="K40" s="23" t="s">
+      <c r="L40" t="s">
         <v>224</v>
       </c>
-      <c r="L40" s="23">
+      <c r="M40">
         <v>40.06</v>
       </c>
-      <c r="M40" s="23" t="s">
+      <c r="N40" t="s">
         <v>218</v>
       </c>
-      <c r="N40" s="23">
+      <c r="O40">
         <v>53.470487599999998</v>
       </c>
-      <c r="O40" s="23">
+      <c r="P40">
         <v>6.8463650999999999</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40" xr:uid="{7CBED238-7D8E-4E5A-8A55-C5BC7EDC270C}"/>
+  <autoFilter ref="A1:P40" xr:uid="{7CBED238-7D8E-4E5A-8A55-C5BC7EDC270C}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
